--- a/static/spark-cv/data/research.xlsx
+++ b/static/spark-cv/data/research.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spark\Documents\spark-webs\spark-web\public\spark-cv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seonggpa\Documents\spark-web\spark-hydro.github.io\static\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFEAE2C-CC84-4425-BDD8-D80AB0458F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FBD4A4-228D-445A-8E72-53395C210D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="38580" windowHeight="20970" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="121">
   <si>
     <t>type</t>
   </si>
@@ -209,9 +209,6 @@
     <t>Developed a graphical user interface, a workflow implemented in QGIS, for application and evaluation of APEX-MODFLOW models</t>
   </si>
   <si>
-    <t>Develop a Carbon dynamics model for predicting GHG emission and sequestration in croplands</t>
-  </si>
-  <si>
     <t>Fortran, Python</t>
   </si>
   <si>
@@ -299,9 +296,6 @@
     <t xml:space="preserve">Park, S., Jeong, J., Hong, Y., and Bailey, R. </t>
   </si>
   <si>
-    <t>Develop a Rice paddy module in SWAT+ for simulating paddy rice cultivation and irrigation management in agricultural watersheds</t>
-  </si>
-  <si>
     <t>swatmf-Hg</t>
   </si>
   <si>
@@ -341,12 +335,6 @@
     <t>Python, SWAT+</t>
   </si>
   <si>
-    <t>Celray, J and Park, S</t>
-  </si>
-  <si>
-    <t>Develop the CoSWAT framework to advance global crop ecosystem and hydrological analysis</t>
-  </si>
-  <si>
     <t>Park, S.</t>
   </si>
   <si>
@@ -372,6 +360,45 @@
   </si>
   <si>
     <t>APEX, AMRS, PEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park, S., and Serrano, D. </t>
+  </si>
+  <si>
+    <t>mf6swatp</t>
+  </si>
+  <si>
+    <t>Developed a Carbon dynamics model for predicting GHG emission and sequestration in croplands</t>
+  </si>
+  <si>
+    <t>Developed a Rice paddy module in SWAT+ for simulating paddy rice cultivation and irrigation management in agricultural watersheds</t>
+  </si>
+  <si>
+    <t>Develop a coupled modeling framework that links MODFLOW 6 and SWAT+ for surface water-groundwater interaction modeling.</t>
+  </si>
+  <si>
+    <t>Park, S. and Serrano, D.</t>
+  </si>
+  <si>
+    <t>Celray, J. and Park, S.</t>
+  </si>
+  <si>
+    <t>Developed the CoSWAT framework to advance global crop ecosystem and hydrological analysis</t>
+  </si>
+  <si>
+    <t>Develop an interactive hydrologic modeling and data visualization platform for the Texas Produced Water Consortium (TxPWC)</t>
+  </si>
+  <si>
+    <t>Python, Javascript, SWAT+</t>
+  </si>
+  <si>
+    <t>TxPWC-Dashboard</t>
+  </si>
+  <si>
+    <t>https://txpwc-dashboard.streamlit.app/</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-hydro/txpwc-dashboard</t>
   </si>
 </sst>
 </file>
@@ -778,21 +805,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80AB2D6-D787-8D4A-BD11-32CAE09CA316}">
-  <dimension ref="A1:N39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="11" style="2"/>
     <col min="5" max="5" width="23.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="62" style="2" customWidth="1"/>
-    <col min="8" max="9" width="25.69921875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.796875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.69921875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="23.796875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="25.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.83203125" style="2" customWidth="1"/>
     <col min="13" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -800,7 +827,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -830,13 +857,13 @@
         <v>15</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>53</v>
       </c>
@@ -850,13 +877,13 @@
         <v>2025</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>53</v>
       </c>
@@ -869,14 +896,17 @@
       <c r="E3" s="2">
         <v>2024</v>
       </c>
+      <c r="F3" s="2">
+        <v>2025</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>53</v>
       </c>
@@ -893,14 +923,14 @@
         <v>2024</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
@@ -917,16 +947,16 @@
         <v>2024</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="62" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>53</v>
       </c>
@@ -943,13 +973,13 @@
         <v>2023</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -966,7 +996,7 @@
         <v>2022</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>10</v>
@@ -975,7 +1005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>53</v>
       </c>
@@ -992,14 +1022,14 @@
         <v>2022</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="62" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>53</v>
       </c>
@@ -1022,7 +1052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>53</v>
       </c>
@@ -1045,7 +1075,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>53</v>
       </c>
@@ -1068,7 +1098,35 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="31" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1076,27 +1134,29 @@
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1">
         <v>2024</v>
       </c>
-      <c r="F14" s="1"/>
+      <c r="F14" s="1">
+        <v>2025</v>
+      </c>
       <c r="G14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="I14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1104,27 +1164,29 @@
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="1">
         <v>2023</v>
       </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1">
+        <v>2025</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="78" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1132,10 +1194,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D16" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1">
         <v>2022</v>
@@ -1144,17 +1206,17 @@
         <v>2024</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1162,10 +1224,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
         <v>2020</v>
@@ -1180,7 +1242,7 @@
         <v>24</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>44</v>
@@ -1188,7 +1250,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -1196,10 +1258,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2">
         <v>2019</v>
@@ -1214,12 +1276,12 @@
         <v>24</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -1227,10 +1289,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2">
         <v>2019</v>
@@ -1245,7 +1307,7 @@
         <v>24</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>45</v>
@@ -1255,17 +1317,17 @@
       </c>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -1273,25 +1335,28 @@
       <c r="E21" s="2">
         <v>2024</v>
       </c>
+      <c r="F21" s="2">
+        <v>2025</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="62" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -1303,32 +1368,32 @@
         <v>2024</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="N22" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:14" ht="62" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -1340,13 +1405,13 @@
         <v>2024</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
@@ -1354,13 +1419,13 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -1368,7 +1433,7 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="2">
         <v>4</v>
@@ -1380,7 +1445,7 @@
         <v>2023</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>46</v>
@@ -1393,7 +1458,7 @@
       </c>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -1401,7 +1466,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D25" s="2">
         <v>5</v>
@@ -1413,7 +1478,7 @@
         <v>2023</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>22</v>
@@ -1426,7 +1491,7 @@
       </c>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -1434,7 +1499,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="D26" s="2">
         <v>6</v>
@@ -1459,7 +1524,7 @@
       </c>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -1467,7 +1532,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="D27" s="2">
         <v>7</v>
@@ -1495,12 +1560,12 @@
       </c>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
     </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" s="1" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -1508,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D29" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="1">
         <v>2018</v>
@@ -1532,7 +1597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="62" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>21</v>
       </c>
@@ -1540,10 +1605,10 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2">
         <v>2021</v>
@@ -1552,7 +1617,7 @@
         <v>2023</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>46</v>
@@ -1565,7 +1630,7 @@
       </c>
       <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>21</v>
       </c>
@@ -1573,10 +1638,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="D31" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="2">
         <v>2021</v>
@@ -1585,7 +1650,7 @@
         <v>2021</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>46</v>
@@ -1598,7 +1663,7 @@
       </c>
       <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>21</v>
       </c>
@@ -1606,10 +1671,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="D32" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2">
         <v>2021</v>
@@ -1618,7 +1683,7 @@
         <v>2021</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>46</v>
@@ -1631,7 +1696,7 @@
       </c>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="31" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>21</v>
       </c>
@@ -1639,105 +1704,146 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2">
         <v>2024</v>
       </c>
+      <c r="F33" s="2">
+        <v>2026</v>
+      </c>
       <c r="G33" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-    </row>
-    <row r="35" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-    </row>
-    <row r="36" spans="1:12" ht="78" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="34" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2026</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+    </row>
+    <row r="37" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" spans="1:12" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="2">
+      <c r="B38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="2">
         <v>1</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E38" s="2">
         <v>2018</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F38" s="2">
         <v>2018</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="G38" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="2">
+    <row r="39" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="2">
         <v>2011</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F39" s="2">
         <v>2012</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="2">
+      <c r="G39" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="B40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2">
         <v>2004</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F40" s="2">
         <v>2006</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="2">
+    <row r="41" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="B41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2">
         <v>2004</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F41" s="2">
         <v>2006</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G41" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H41" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1765,8 +1871,10 @@
     <hyperlink ref="J5" r:id="rId20" xr:uid="{E2C4FF68-D3C8-B546-A164-991490621EA5}"/>
     <hyperlink ref="K32" r:id="rId21" xr:uid="{0B5297EE-ECF4-A645-8815-E0AA6996F8C9}"/>
     <hyperlink ref="J32" r:id="rId22" xr:uid="{3443909C-BB9C-7D41-840A-9D64924CC32F}"/>
+    <hyperlink ref="J34" r:id="rId23" xr:uid="{495B14B3-44DB-47EE-83A6-FB45E5B5DFD7}"/>
+    <hyperlink ref="K34" r:id="rId24" xr:uid="{B52B153D-2983-4CCC-87C6-187621B62B2C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId23"/>
+  <pageSetup orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>